--- a/data/Lead_information_Formulario_Chile_Main.xlsx
+++ b/data/Lead_information_Formulario_Chile_Main.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,38 +481,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.cl/flotas/planes-leasing</t>
+          <t>https://www.chevrolet.cl/autos-electricos/blazer-rs-ev/evento</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/flotas-leasing</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/evento-blazer-rs-ev?model=blazer%20rs%20ev</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>blazer rs ev</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Perez</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6161057K</t>
+          <t>166771188</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>925610630</t>
+          <t>966284785</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>carlosperez_cl16@mrm.com</t>
+          <t>emilioherrera_cl29@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -520,132 +524,6 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.chevrolet.cl/autos-electricos/blazer-rs-ev/evento</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/evento-blazer-rs-ev?model=blazer%20rs%20ev</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Herrera</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>166771188</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>966284785</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>emilioherrera_cl29@mrm.com</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.chevrolet.cl/autos-electricos/captiva-ev</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/captiva-ev?model=captiva%20ev</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Romina Florencia</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Diaz</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>111707472</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>949151172</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>rominaflorenciadiaz_cl96@mrm.com</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.chevrolet.cl/solicitar-cotizacion</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/raq-nuevo</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Florencia Valentina</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Villanueva</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>179433516</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>961345509</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>florenciavalentinavillanueva_cl38@mrm.com</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Lead_information_Formulario_Chile_Main.xlsx
+++ b/data/Lead_information_Formulario_Chile_Main.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,42 +481,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.cl/autos-electricos/blazer-rs-ev/evento</t>
+          <t>https://www.chevrolet.cl/autos-electricos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/evento-blazer-rs-ev?model=blazer%20rs%20ev</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>blazer rs ev</t>
-        </is>
-      </c>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/electricos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Nicolás</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Mamani</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>166771188</t>
+          <t>19076995K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>966284785</t>
+          <t>961784596</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>emilioherrera_cl29@mrm.com</t>
+          <t>nicolasmamani_cl05@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -524,6 +520,132 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.cl/camiones</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/camiones-raq</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Alejandro Verónica</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>235157799</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>936356461</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>alejandroveronicaflores_cl79@mrm.com</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.cl/autos-electricos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/electricos</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Javier Carolina</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Espinoza Sanchez</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>176342943</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>927017121</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>javiercarolinaespinozasanchez.cl87@mrm.com</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.cl/solicitar-cotizacion</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/raq-nuevo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Marcelo Sandra</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>22599840K</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>937509979</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>marcelosandrabravo.cl36@mrm.com</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Lead_information_Formulario_Chile_Main.xlsx
+++ b/data/Lead_information_Formulario_Chile_Main.xlsx
@@ -481,38 +481,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.cl/autos-electricos</t>
+          <t>https://www.chevrolet.cl/formulario-de-contacto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/electricos</t>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/posventa-formulario-de-contacto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nicolás</t>
+          <t>Romina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mamani</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19076995K</t>
+          <t>6808900K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>961784596</t>
+          <t>952182156</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>nicolasmamani_cl05@mrm.com</t>
+          <t>rominapinto_cl33@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,38 +523,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.cl/camiones</t>
+          <t>https://www.chevrolet.cl/campanas-de-seguridad/takata-airbag-conductor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/camiones-raq</t>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/campanas-de-seguridad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alejandro Verónica</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Flores</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>235157799</t>
+          <t>186518020</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>936356461</t>
+          <t>974904954</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>alejandroveronicaflores_cl79@mrm.com</t>
+          <t>luismartinez.cl20@mrm.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -565,38 +565,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.cl/autos-electricos</t>
+          <t>https://www.chevrolet.cl/mantenciones/mantenciones-prepagadas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/chile/gm_forms/electricos</t>
+          <t>https://secure-developments.com/commonwealth/chile/gm_forms/mantenimiento-prepagado?model=mantenimiento</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Javier Carolina</t>
+          <t>Tomás Camila</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Espinoza Sanchez</t>
+          <t>Ruiz Muñoz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>176342943</t>
+          <t>14291784K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>927017121</t>
+          <t>969369165</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>javiercarolinaespinozasanchez.cl87@mrm.com</t>
+          <t>tomascamilaruizmunoz_cl30@mrm.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -618,27 +618,27 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Marcelo Sandra</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Contreras Guerrero</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22599840K</t>
+          <t>174511160</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>937509979</t>
+          <t>997230023</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>marcelosandrabravo.cl36@mrm.com</t>
+          <t>nataliacontrerasguerrero_cl16@mrm.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
